--- a/光伏配储项目/电价数据/2026/银湖站.xlsx
+++ b/光伏配储项目/电价数据/2026/银湖站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.53654</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.23549</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64237</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.81686</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.71396</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4402799999999999</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45601</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44568</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.75483</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.60724</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.50851</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.56171</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.58739</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.80503</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.8067000000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.80964</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.49131</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.16172</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.53507</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.5322899999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.80045</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.9111699999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5913999999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.6454299999999999</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.62582</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.79464</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.74346</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.8027000000000001</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.04317</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.32272</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.46764</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.71498</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.16373</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.97668</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.83601</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.99205</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.18096</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9448</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.71395</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.75877</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.4295</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.15098</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.75915</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.10836</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.20355</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.06194</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.43461</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.18434</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.16936</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.12582</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.72617</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47934</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42214</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.07624</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.96069</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.04108</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5347499999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41027</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47236</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42094</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.75654</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72394</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.83527</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.97907</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.6152799999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.7988200000000001</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.8405900000000001</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.7372300000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.6353799999999999</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.48742</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.50924</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.62051</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.03238</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.05912</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.34119</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.99124</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.2614</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.87026</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.79464</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.19195</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.01728</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.9164</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.50346</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.49812</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.58648</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47984</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5046499999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.11099</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.95808</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92392</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.94738</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.85287</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7838999999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.80318</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.56195</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.8902</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.10411</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04798</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.87364</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.25143</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.48639</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.42633</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.50415</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.60244</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.58613</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.74812</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.09846</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.20313</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.93047</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.66077</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.63017</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33348</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5154500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54162</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43329</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47329</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44398</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.62652</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.64386</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.65663</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6126699999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.60911</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.46902</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.49324</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.6941799999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9154600000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.26049</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.61294</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.98593</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.32373</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.82914</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.87929</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.68413</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8188</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.9675499999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.9516100000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6938099999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.52112</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.9267799999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.8656200000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.97115</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.5362</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.15441</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.14963</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.97496</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.91644</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.86314</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.31337</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.26492</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.13262</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.09675</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.14971</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.09174</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.04098</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.91749</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.56648</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.91555</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9364199999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.92249</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.01752</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.9458300000000001</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.04933</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.8757200000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.6713899999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.65463</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.49856</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9117000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.49137</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.46804</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.58486</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.56959</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46642</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5771799999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.54816</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6717799999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.90798</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.9698300000000001</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.67203</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.05566</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.10073</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.64336</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.72961</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.00343</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.9827899999999999</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.20741</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.84554</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.90524</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.54599</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.68448</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.47938</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.5341</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.82087</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.9692200000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.80976</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.83813</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.86633</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.8032</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.76487</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.72882</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.95289</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.00635</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.6091</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.9667100000000001</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.90823</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.64493</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.82753</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.87426</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.89925</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.9776699999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.99536</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9617899999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.61503</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.90983</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.8703099999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.82396</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.89699</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.9317799999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.9275099999999999</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.90019</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.6025900000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.61052</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31163</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.5678300000000001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.46285</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.21283</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.24828</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.20805</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.17735</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.22312</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.23941</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.46592</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.17548</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.17106</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.46349</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17185</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18423</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.21386</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.20396</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.2033</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.16009</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.17784</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.19004</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.16866</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.51271</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.42554</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.43523</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.44145</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.46238</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31119</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.01368</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.77211</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.80033</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5330499999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.51607</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.22372</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06504</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.16678</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04426</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20569</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04946</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06059</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04275</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01517</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0445</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04195</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.16507</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04234</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.16554</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.16562</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.16785</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.17874</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.18513</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.18532</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.18757</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33589</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.38765</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30159</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.27234</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.6193500000000001</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.7279600000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.5732200000000001</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5467000000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.59436</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.6445599999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.7934</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48443</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.63855</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.6333799999999999</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.7476699999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.51414</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.46836</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14203</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.60149</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.60542</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.5503400000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.5402</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.6650700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7965399999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7365499999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5428200000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.67169</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.95136</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.2666</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.74297</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.28726</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.26016</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.67729</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.67392</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.24691</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.92372</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.6323</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.24651</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.71957</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.6485</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.33136</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.71239</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8044600000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78828</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88093</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5057900000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41618</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22329</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6392899999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54237</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42595</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45257</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45067</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59514</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43365</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58411</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66574</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.8147300000000001</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.56989</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55453</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.28545</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8737999999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.14992</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.12703</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.09361</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.47413</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.6437200000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.53228</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.4689700000000001</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.66899</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5717899999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.51737</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.48633</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.8132200000000001</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.67813</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.37992</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5362</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5485800000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.42716</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.5200399999999999</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.51064</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.5372400000000001</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.55655</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.50437</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.53435</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.5305800000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.46701</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5468200000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.63558</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.5355599999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.62748</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.54867</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.54332</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5537000000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.5334099999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.5207999999999999</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.50785</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.51718</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46828</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41463</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35304</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95587</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47608</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47777</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5400499999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40692</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.57725</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.52473</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.6060099999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.7137899999999999</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.88012</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.68979</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.80611</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.6848500000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.76249</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.6971799999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5477799999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.66422</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.8079500000000001</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.71905</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.13891</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.7292999999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.94592</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.65461</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.66952</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.53299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.18192</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.6190599999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.39763</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.47163</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.75274</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.07703</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.7422</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.36811</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.63907</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.8974299999999999</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.72854</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.54634</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.1027</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.5779299999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.10836</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.42464</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.97134</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.16346</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.71661</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.50371</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.1783</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.02738</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.8397899999999999</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.8212699999999999</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.79743</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.81459</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.25352</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.06996</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.66616</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.05101</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.59863</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.82625</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.80675</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.69051</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.7383200000000001</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.7172999999999999</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.86337</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.88322</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.71476</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.89134</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.16089</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.80538</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.9010499999999999</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.7683099999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.79123</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.13783</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.77511</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.7912400000000001</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.86388</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.7377899999999999</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.72542</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.34661</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.90564</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.49952</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.25378</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.81221</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.82099</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.6497999999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.72663</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6636299999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26316</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.5482</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40244</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29229</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.44117</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.5355</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5400199999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.48422</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.59575</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.81086</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7603099999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.60297</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.5401</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.65749</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.77643</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.76291</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.64225</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.45216</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.49068</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.57084</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7136699999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.7143200000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.70304</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.70529</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.00813</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.00887</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.6401699999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.75703</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.17823</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.6839700000000001</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.16239</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.04252</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.03524</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.10261</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.81402</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.28062</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.44692</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.81141</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.77787</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.69626</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.03485</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.01792</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.05136</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.06471</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.05982</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.03695</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.06141</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.80872</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.09452</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.30848</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.17594</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.1994</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.09151</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.09925</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.10734</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.04427</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.14163</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6918800000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.75305</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.08534</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.09371</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.0876</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.64666</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.16704</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.48394</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.11724</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.25481</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61509</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.52401</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.6532</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.13324</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.41337</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32404</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.75587</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.5590499999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.56353</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.56737</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.65877</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.80955</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.6451399999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.56102</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44209</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.5664199999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.10943</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42513</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38603</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56321</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.54599</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.4202</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38505</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47183</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.5734400000000001</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.55263</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.5843200000000001</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.18511</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.28062</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26825</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.53365</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.7300099999999999</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.72333</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.98964</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.8024600000000001</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.6665099999999999</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.8035099999999999</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.61068</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.83785</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.7869700000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.65261</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.15054</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.70427</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.91054</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.55731</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.01472</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.6087400000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.94624</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.13044</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.8979299999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.6584800000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.15945</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9592000000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.77716</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40861</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41824</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5603899999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5005299999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.11793</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.65134</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.72513</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.79945</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.53692</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.47847</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.66512</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.46841</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.51507</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.51135</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74093</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.7885</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.85565</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.34214</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.69666</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.44635</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.38689</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.30924</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.17809</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.87109</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.74902</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.12388</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.49879</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.52079</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.64339</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.91677</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.60533</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.7788999999999999</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.58872</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.79713</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.78711</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.2812</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.2409</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.9297300000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.93088</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.0821</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.06446</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.43227</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.73647</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.53685</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.11443</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.18895</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.74098</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.77206</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.94911</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.15011</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8303200000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47797</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47137</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.01518</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.61275</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48075</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.49755</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.6115700000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.5849800000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.5860700000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.9700299999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.87101</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.24652</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.09945</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.65137</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.69794</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7086399999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.46981</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.41911</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.45223</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.47453</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.47264</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42889</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5053500000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.48652</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.54976</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36415</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.64115</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.52699</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39406</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.19703</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25723</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.19399</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25709</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.20401</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.25235</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24549</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.52507</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44178</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.49952</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35167</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.59233</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.20381</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.24804</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.19953</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.18356</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.17886</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.19757</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.17738</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.21936</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.53543</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.17213</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.17967</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.20103</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.17119</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.17984</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.17121</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.18509</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.17834</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.22316</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.28368</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.64286</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32568</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.84275</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.87376</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.49315</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.55536</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.52776</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.41856</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.62001</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.56287</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.92218</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9252400000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.04458</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8904099999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.71212</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.96348</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10238</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.47567</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22325</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.46258</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.48817</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.18654</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.70214</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5262899999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.48751</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.81853</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.47053</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.62258</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.5446799999999999</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.95187</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.74294</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.7415</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.74974</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.75849</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.8984500000000001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5571900000000001</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7902899999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.5932000000000001</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.81662</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.2444</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.24723</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.27878</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.70431</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.24486</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.34556</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.42585</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.94494</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7928999999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84402</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.84134</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.00614</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7830499999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5970800000000001</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33773</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.4825</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.64149</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.47297</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.59858</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.59956</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47494</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27039</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38786</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.8408</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.69997</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6391</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48831</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51625</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.80026</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.9080900000000001</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.82067</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.91091</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.26881</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.26348</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.83173</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.84965</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.5995</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.45982</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.51066</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46563</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.45531</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.53259</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.08501</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.7027899999999999</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.45924</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.42088</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.43317</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.47853</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.45878</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40867</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.48429</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.55357</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.9037999999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.8549600000000001</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.55291</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.48197</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.9971100000000001</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.69486</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.58427</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9022</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.7323</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.46326</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45457</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33929</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43428</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.53631</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.5900700000000001</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5635599999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.83802</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.53718</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.76313</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.6762400000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.7915599999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.83057</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.77947</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7520800000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.78587</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.7645</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.75385</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.75701</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.1794</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.47598</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.74759</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.51922</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.75822</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.76581</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.59657</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.7476499999999999</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.62809</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.76086</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7331299999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.7626900000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.04957</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.21044</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.23297</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.28041</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.3472</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.33024</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.40001</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.41246</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.3904</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.98502</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.87738</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.8395199999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.48064</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.0526</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.8132999999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.89891</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.76622</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.69499</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.68248</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.68887</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6523300000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.68576</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55176</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45847</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.5825199999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.65343</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6162799999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36868</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.68759</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69574</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.5500700000000001</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.70787</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.60724</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6077100000000001</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5230199999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.64131</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.65191</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.8351000000000001</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.69287</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.83368</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.76497</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.84169</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.82448</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.82462</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.04127</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06023</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.8014</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5047699999999999</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.58788</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.61258</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.6897799999999999</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.67204</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.72646</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.22491</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.22701</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.52026</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.24785</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.52391</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.50556</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.53754</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.35322</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.27793</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.91512</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.89563</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.56653</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.63996</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.30685</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.30832</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13074</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.55198</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.64265</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.61796</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.06739</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.03499</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.77176</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.27714</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.25559</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.53182</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.29877</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.30056</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.6687000000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.65167</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.63912</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37507</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.59776</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.58521</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.88127</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.70539</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.6352300000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.6616000000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.82686</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.8446699999999999</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.96396</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5657000000000001</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.26011</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.02187</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.9778</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.6736599999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.47701</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17197</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.33881</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6611</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.6635800000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.7444400000000001</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.6550499999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.75809</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.52938</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.43437</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.84535</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.67264</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.57152</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.62575</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.7553</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.84293</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.89899</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.75964</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.77027</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.75552</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.75175</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.76236</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.10875</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.14885</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.05148</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.07062</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.24807</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.00595</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.03962</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.82108</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.80153</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.81757</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.85729</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.85858</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.8398</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.94974</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6205499999999999</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.59039</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.5347999999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37537</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.31158</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.91331</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9392699999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.22094</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.7693</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45338</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.6349199999999999</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.50581</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.59988</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.60097</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.7230700000000001</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.7285499999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.29368</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.78599</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.86407</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9699800000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.95762</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.85488</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.06433</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.8097000000000001</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.46862</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.17683</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.44258</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8360700000000001</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5367799999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.63503</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.82996</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.59805</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.44779</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.5298999999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.9920800000000001</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.80811</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.59504</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.27532</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.85872</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.84524</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.39644</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.23824</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.05293</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.9039199999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.8727200000000001</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.8802300000000001</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.87575</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.8998400000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.90019</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.9361799999999999</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.37013</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.41593</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.51859</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.85439</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.87675</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.85748</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.9000199999999999</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.67613</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.07693</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.62879</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.60642</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.48469</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.98878</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.64466</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.64637</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.47192</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.47454</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.44871</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.46105</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.44237</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.74019</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5755800000000001</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.87113</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.15429</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.8166599999999999</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.87139</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.54518</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.51849</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.41131</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.4966</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.28416</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.89078</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.68888</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.48913</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.5720700000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.52271</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.69563</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5377000000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.86091</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.7443</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.75544</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.78167</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.80016</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.58693</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.5591799999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.54025</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5553400000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.56209</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.57747</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.64335</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.6465599999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.64547</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.93063</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.67774</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.57467</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.58663</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.56828</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5315299999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5303099999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.66539</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.63762</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6982200000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.5738300000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5286799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47729</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.45873</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
